--- a/output/xlsx/LoginServidorAdministrador--GT-.xlsx
+++ b/output/xlsx/LoginServidorAdministrador--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="55">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -105,6 +105,12 @@
   </si>
   <si>
     <t>SYSTEM exibe pagina 'Search extraction'</t>
+  </si>
+  <si>
+    <t>administrador: abre outro navegador na pagina de login e insere user e password do usuario ja logado</t>
+  </si>
+  <si>
+    <t>SYSTEM desloga o usuario na pagina anterior e continua sua sessao na nova pagina</t>
   </si>
   <si>
     <t xml:space="preserve">Postcondition: </t>
@@ -262,7 +268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
@@ -406,98 +412,98 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="1">
+      <c r="A12" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B12" t="s" s="3">
         <v>31</v>
       </c>
-      <c r="B12" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B15" t="s" s="0">
+      <c r="C12" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s" s="3">
         <v>32</v>
       </c>
-      <c r="C15" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E15" t="s" s="1">
-        <v>14</v>
+      <c r="E12" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F12" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="C16" t="s" s="1">
+        <v>13</v>
       </c>
       <c r="E16" t="s" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E17" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="B18" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
+    <row r="19">
+      <c r="A19" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B18" t="s" s="2">
+      <c r="B19" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C18" t="s" s="2">
+      <c r="C19" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D18" t="s" s="2">
+      <c r="D19" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E18" t="s" s="2">
+      <c r="E19" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F18" t="s" s="2">
+      <c r="F19" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B19" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C19" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D19" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E19" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F19" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n" s="4">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="B20" t="s" s="3">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D20" t="s" s="3">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s" s="3">
         <v>27</v>
@@ -508,474 +514,534 @@
     </row>
     <row r="21">
       <c r="A21" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B21" t="s" s="3">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s" s="3">
+        <v>37</v>
+      </c>
+      <c r="E21" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F21" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n" s="4">
         <v>3.0</v>
       </c>
-      <c r="B21" t="s" s="3">
+      <c r="B22" t="s" s="3">
         <v>29</v>
       </c>
-      <c r="C21" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D21" t="s" s="3">
+      <c r="C22" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s" s="3">
         <v>30</v>
       </c>
-      <c r="E21" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F21" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="1">
+      <c r="E22" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F22" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B23" t="s" s="3">
         <v>31</v>
       </c>
-      <c r="B22" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B25" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="C25" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E25" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="E26" t="s" s="1">
-        <v>17</v>
+      <c r="C23" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F23" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C27" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E28" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B27" t="s" s="0">
+      <c r="B29" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
+    <row r="30">
+      <c r="A30" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B28" t="s" s="2">
+      <c r="B30" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C28" t="s" s="2">
+      <c r="C30" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D28" t="s" s="2">
+      <c r="D30" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E28" t="s" s="2">
+      <c r="E30" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F28" t="s" s="2">
+      <c r="F30" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B29" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C29" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D29" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E29" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F29" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B30" t="s" s="3">
-        <v>38</v>
-      </c>
-      <c r="C30" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D30" t="s" s="3">
-        <v>39</v>
-      </c>
-      <c r="E30" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F30" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B31" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D31" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E31" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F31" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B32" t="s" s="3">
+        <v>40</v>
+      </c>
+      <c r="C32" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D32" t="s" s="3">
+        <v>41</v>
+      </c>
+      <c r="E32" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F32" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n" s="4">
         <v>3.0</v>
       </c>
-      <c r="B31" t="s" s="3">
+      <c r="B33" t="s" s="3">
         <v>29</v>
       </c>
-      <c r="C31" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D31" t="s" s="3">
+      <c r="C33" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D33" t="s" s="3">
         <v>30</v>
       </c>
-      <c r="E31" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F31" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="1">
+      <c r="E33" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F33" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B34" t="s" s="3">
         <v>31</v>
       </c>
-      <c r="B32" t="s" s="0">
+      <c r="C34" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D34" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E34" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F34" t="s" s="3">
         <v>27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="1">
         <v>11</v>
       </c>
-      <c r="B35" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="C35" t="s" s="1">
+      <c r="B38" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C38" t="s" s="1">
         <v>13</v>
       </c>
-      <c r="E35" t="s" s="1">
+      <c r="E38" t="s" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="s" s="1">
+    <row r="39">
+      <c r="A39" t="s" s="1">
         <v>15</v>
       </c>
-      <c r="B36" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="E36" t="s" s="1">
+      <c r="B39" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E39" t="s" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="s" s="1">
+    <row r="40">
+      <c r="A40" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B37" t="s" s="0">
+      <c r="B40" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
+    <row r="41">
+      <c r="A41" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B38" t="s" s="2">
+      <c r="B41" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C38" t="s" s="2">
+      <c r="C41" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D38" t="s" s="2">
+      <c r="D41" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E38" t="s" s="2">
+      <c r="E41" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F38" t="s" s="2">
+      <c r="F41" t="s" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n" s="4">
+    <row r="42">
+      <c r="A42" t="n" s="4">
         <v>1.0</v>
       </c>
-      <c r="B39" t="s" s="3">
+      <c r="B42" t="s" s="3">
         <v>26</v>
       </c>
-      <c r="C39" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D39" t="s" s="3">
+      <c r="C42" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D42" t="s" s="3">
         <v>28</v>
       </c>
-      <c r="E39" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F39" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n" s="4">
+      <c r="E42" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F42" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n" s="4">
         <v>2.0</v>
       </c>
-      <c r="B40" t="s" s="3">
-        <v>42</v>
-      </c>
-      <c r="C40" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D40" t="s" s="3">
-        <v>43</v>
-      </c>
-      <c r="E40" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F40" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n" s="4">
+      <c r="B43" t="s" s="3">
+        <v>44</v>
+      </c>
+      <c r="C43" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D43" t="s" s="3">
+        <v>45</v>
+      </c>
+      <c r="E43" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F43" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n" s="4">
         <v>3.0</v>
       </c>
-      <c r="B41" t="s" s="3">
-        <v>44</v>
-      </c>
-      <c r="C41" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D41" t="s" s="3">
-        <v>45</v>
-      </c>
-      <c r="E41" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F41" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="B42" t="s" s="0">
+      <c r="B44" t="s" s="3">
+        <v>46</v>
+      </c>
+      <c r="C44" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D44" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="E44" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F44" t="s" s="3">
         <v>27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="1">
         <v>11</v>
       </c>
-      <c r="B45" t="s" s="0">
-        <v>46</v>
-      </c>
-      <c r="C45" t="s" s="1">
+      <c r="B48" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C48" t="s" s="1">
         <v>13</v>
       </c>
-      <c r="E45" t="s" s="1">
+      <c r="E48" t="s" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="s" s="1">
+    <row r="49">
+      <c r="A49" t="s" s="1">
         <v>15</v>
       </c>
-      <c r="B46" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="E46" t="s" s="1">
+      <c r="B49" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E49" t="s" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="s" s="1">
+    <row r="50">
+      <c r="A50" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B47" t="s" s="0">
+      <c r="B50" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
+    <row r="51">
+      <c r="A51" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B48" t="s" s="2">
+      <c r="B51" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C48" t="s" s="2">
+      <c r="C51" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D48" t="s" s="2">
+      <c r="D51" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E48" t="s" s="2">
+      <c r="E51" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F48" t="s" s="2">
+      <c r="F51" t="s" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n" s="4">
+    <row r="52">
+      <c r="A52" t="n" s="4">
         <v>1.0</v>
       </c>
-      <c r="B49" t="s" s="3">
+      <c r="B52" t="s" s="3">
         <v>26</v>
       </c>
-      <c r="C49" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D49" t="s" s="3">
+      <c r="C52" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D52" t="s" s="3">
         <v>28</v>
       </c>
-      <c r="E49" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F49" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n" s="4">
+      <c r="E52" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F52" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n" s="4">
         <v>2.0</v>
       </c>
-      <c r="B50" t="s" s="3">
+      <c r="B53" t="s" s="3">
         <v>29</v>
       </c>
-      <c r="C50" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D50" t="s" s="3">
-        <v>48</v>
-      </c>
-      <c r="E50" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F50" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="B51" t="s" s="0">
-        <v>49</v>
+      <c r="C53" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D53" t="s" s="3">
+        <v>50</v>
+      </c>
+      <c r="E53" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F53" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="1">
         <v>11</v>
       </c>
-      <c r="B54" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="C54" t="s" s="1">
+      <c r="B57" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C57" t="s" s="1">
         <v>13</v>
       </c>
-      <c r="E54" t="s" s="1">
+      <c r="E57" t="s" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="s" s="1">
+    <row r="58">
+      <c r="A58" t="s" s="1">
         <v>15</v>
       </c>
-      <c r="B55" t="s" s="0">
+      <c r="B58" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="E58" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D60" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B61" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C61" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D61" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E61" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F61" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B62" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C62" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D62" t="s" s="3">
+        <v>54</v>
+      </c>
+      <c r="E62" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F62" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B63" t="s" s="0">
         <v>51</v>
-      </c>
-      <c r="E55" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B56" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D57" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E57" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F57" t="s" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B58" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C58" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D58" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E58" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F58" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B59" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C59" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D59" t="s" s="3">
-        <v>52</v>
-      </c>
-      <c r="E59" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F59" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="B60" t="s" s="0">
-        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/output/xlsx/LoginServidorAdministrador--GT-.xlsx
+++ b/output/xlsx/LoginServidorAdministrador--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="44">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -38,7 +38,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 5 test case(s)</t>
+    <t>Size: 4 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -144,21 +144,6 @@
   </si>
   <si>
     <t>SYSTEM informa que usuário está bloqueado</t>
-  </si>
-  <si>
-    <t>TC5</t>
-  </si>
-  <si>
-    <t>Exception Flow 3: Usuario inativo por 30 minutos</t>
-  </si>
-  <si>
-    <t>system: SYSTEM: finaliza sessao do usuario e retorna a pagina de login</t>
-  </si>
-  <si>
-    <t>finaliza sessao do usuario e retorna a pagina de login</t>
-  </si>
-  <si>
-    <t>Flow interrupted due to exception / error</t>
   </si>
 </sst>
 </file>
@@ -250,7 +235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
@@ -684,87 +669,6 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B41" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="C41" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E41" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="E42" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B43" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D44" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E44" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F44" t="s" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B45" t="s" s="3">
-        <v>46</v>
-      </c>
-      <c r="C45" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D45" t="s" s="3">
-        <v>47</v>
-      </c>
-      <c r="E45" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F45" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="B46" t="s" s="0">
-        <v>48</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/output/xlsx/LoginServidorAdministrador--GT-.xlsx
+++ b/output/xlsx/LoginServidorAdministrador--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="42">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -138,12 +138,6 @@
   </si>
   <si>
     <t>SYSTEM bloqueia a sessão</t>
-  </si>
-  <si>
-    <t>administrador: digita o login e pasword válidos do usuário bloqueado e pressiona o botão Login</t>
-  </si>
-  <si>
-    <t>SYSTEM informa que usuário está bloqueado</t>
   </si>
 </sst>
 </file>
@@ -646,13 +640,13 @@
         <v>2.0</v>
       </c>
       <c r="B37" t="s" s="3">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C37" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D37" t="s" s="3">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E37" t="s" s="3">
         <v>27</v>
